--- a/docs/pension_data_combined_2026-08-06.xlsx
+++ b/docs/pension_data_combined_2026-08-06.xlsx
@@ -1228,7 +1228,7 @@
         <v>1.1701</v>
       </c>
       <c r="D48" t="n">
-        <v>3710883.91</v>
+        <v>3726328.53</v>
       </c>
     </row>
     <row r="49">
@@ -1246,7 +1246,7 @@
         <v>2.1897</v>
       </c>
       <c r="D49" t="n">
-        <v>70105531.87</v>
+        <v>70041892.48</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.2081</v>
       </c>
       <c r="D50" t="n">
-        <v>229893744.61</v>
+        <v>229904036.5</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.2262</v>
       </c>
       <c r="D51" t="n">
-        <v>352767466.36</v>
+        <v>352760155.6</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2305</v>
       </c>
       <c r="D52" t="n">
-        <v>431751590.27</v>
+        <v>431780010.2</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9931</v>
       </c>
       <c r="D53" t="n">
-        <v>397408920.51</v>
+        <v>397408825.9</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.554</v>
       </c>
       <c r="D54" t="n">
-        <v>327780855.29</v>
+        <v>327360947.8</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.2103</v>
       </c>
       <c r="D55" t="n">
-        <v>60908907.02</v>
+        <v>60850794.77</v>
       </c>
     </row>
   </sheetData>
